--- a/data/german_works.xlsx
+++ b/data/german_works.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,6 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,15 +469,10 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>date_mid</t>
+          <t>matiere</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>matiere</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>is_heldenepik</t>
         </is>
@@ -504,15 +498,12 @@
       <c r="E2" t="n">
         <v>1300</v>
       </c>
-      <c r="F2" t="n">
-        <v>1276</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -536,15 +527,12 @@
       <c r="E3" t="n">
         <v>1400</v>
       </c>
-      <c r="F3" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H3" t="b">
+      <c r="G3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -568,15 +556,12 @@
       <c r="E4" t="n">
         <v>1260</v>
       </c>
-      <c r="F4" t="n">
-        <v>1256</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -600,15 +585,12 @@
       <c r="E5" t="n">
         <v>1500</v>
       </c>
-      <c r="F5" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H5" t="b">
+      <c r="G5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -632,15 +614,12 @@
       <c r="E6" t="n">
         <v>1500</v>
       </c>
-      <c r="F6" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H6" t="b">
+      <c r="G6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -664,15 +643,12 @@
       <c r="E7" t="n">
         <v>1475</v>
       </c>
-      <c r="F7" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -696,15 +672,12 @@
       <c r="E8" t="n">
         <v>1250</v>
       </c>
-      <c r="F8" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H8" t="b">
+      <c r="G8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -728,15 +701,12 @@
       <c r="E9" t="n">
         <v>1400</v>
       </c>
-      <c r="F9" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H9" t="b">
+      <c r="G9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -760,15 +730,12 @@
       <c r="E10" t="n">
         <v>1472</v>
       </c>
-      <c r="F10" t="n">
-        <v>1336</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -792,15 +759,12 @@
       <c r="E11" t="n">
         <v>1255</v>
       </c>
-      <c r="F11" t="n">
-        <v>1230</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -824,15 +788,12 @@
       <c r="E12" t="n">
         <v>1474</v>
       </c>
-      <c r="F12" t="n">
-        <v>1412</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -856,15 +817,12 @@
       <c r="E13" t="n">
         <v>1300</v>
       </c>
-      <c r="F13" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -888,15 +846,12 @@
       <c r="E14" t="n">
         <v>1250</v>
       </c>
-      <c r="F14" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -920,15 +875,12 @@
       <c r="E15" t="n">
         <v>1400</v>
       </c>
-      <c r="F15" t="n">
-        <v>1388</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H15" t="b">
+      <c r="G15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -952,15 +904,12 @@
       <c r="E16" t="n">
         <v>1400</v>
       </c>
-      <c r="F16" t="n">
-        <v>1357</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -984,15 +933,12 @@
       <c r="E17" t="n">
         <v>1300</v>
       </c>
-      <c r="F17" t="n">
-        <v>1286</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H17" t="b">
+      <c r="G17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1016,15 +962,12 @@
       <c r="E18" t="n">
         <v>1300</v>
       </c>
-      <c r="F18" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1048,15 +991,12 @@
       <c r="E19" t="n">
         <v>1300</v>
       </c>
-      <c r="F19" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1080,15 +1020,12 @@
       <c r="E20" t="n">
         <v>1500</v>
       </c>
-      <c r="F20" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1112,15 +1049,12 @@
       <c r="E21" t="n">
         <v>1400</v>
       </c>
-      <c r="F21" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1144,15 +1078,12 @@
       <c r="E22" t="n">
         <v>840</v>
       </c>
-      <c r="F22" t="n">
-        <v>770</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1176,15 +1107,12 @@
       <c r="E23" t="n">
         <v>1450</v>
       </c>
-      <c r="F23" t="n">
-        <v>1426</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H23" t="b">
+      <c r="G23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1208,15 +1136,12 @@
       <c r="E24" t="n">
         <v>1400</v>
       </c>
-      <c r="F24" t="n">
-        <v>1376</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1240,15 +1165,12 @@
       <c r="E25" t="n">
         <v>1350</v>
       </c>
-      <c r="F25" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1272,15 +1194,12 @@
       <c r="E26" t="n">
         <v>1400</v>
       </c>
-      <c r="F26" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H26" t="b">
+      <c r="G26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1304,15 +1223,12 @@
       <c r="E27" t="n">
         <v>1350</v>
       </c>
-      <c r="F27" t="n">
-        <v>1326</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H27" t="b">
+      <c r="G27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1336,15 +1252,12 @@
       <c r="E28" t="n">
         <v>1200</v>
       </c>
-      <c r="F28" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1368,15 +1281,12 @@
       <c r="E29" t="n">
         <v>1300</v>
       </c>
-      <c r="F29" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1400,15 +1310,12 @@
       <c r="E30" t="n">
         <v>1250</v>
       </c>
-      <c r="F30" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H30" t="b">
+      <c r="G30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1432,15 +1339,12 @@
       <c r="E31" t="n">
         <v>1300</v>
       </c>
-      <c r="F31" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1464,15 +1368,12 @@
       <c r="E32" t="n">
         <v>1450</v>
       </c>
-      <c r="F32" t="n">
-        <v>1375</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H32" t="b">
+      <c r="G32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1496,15 +1397,12 @@
       <c r="E33" t="n">
         <v>1289</v>
       </c>
-      <c r="F33" t="n">
-        <v>1286</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H33" t="b">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1528,15 +1426,12 @@
       <c r="E34" t="n">
         <v>1280</v>
       </c>
-      <c r="F34" t="n">
-        <v>1276</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1560,15 +1455,12 @@
       <c r="E35" t="n">
         <v>1460</v>
       </c>
-      <c r="F35" t="n">
-        <v>1456</v>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H35" t="b">
+      <c r="G35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1592,15 +1484,12 @@
       <c r="E36" t="n">
         <v>1230</v>
       </c>
-      <c r="F36" t="n">
-        <v>1216</v>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H36" t="b">
+      <c r="G36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1624,15 +1513,12 @@
       <c r="E37" t="n">
         <v>1450</v>
       </c>
-      <c r="F37" t="n">
-        <v>1426</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H37" t="b">
+      <c r="G37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1656,15 +1542,12 @@
       <c r="E38" t="n">
         <v>1210</v>
       </c>
-      <c r="F38" t="n">
-        <v>1196</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H38" t="b">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1688,15 +1571,12 @@
       <c r="E39" t="n">
         <v>1500</v>
       </c>
-      <c r="F39" t="n">
-        <v>1476</v>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H39" t="b">
+      <c r="G39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1720,15 +1600,12 @@
       <c r="E40" t="n">
         <v>1255</v>
       </c>
-      <c r="F40" t="n">
-        <v>1230</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H40" t="b">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1752,15 +1629,12 @@
       <c r="E41" t="n">
         <v>1475</v>
       </c>
-      <c r="F41" t="n">
-        <v>1438</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H41" t="b">
+      <c r="G41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1784,15 +1658,12 @@
       <c r="E42" t="n">
         <v>1500</v>
       </c>
-      <c r="F42" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H42" t="b">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1816,15 +1687,12 @@
       <c r="E43" t="n">
         <v>1296</v>
       </c>
-      <c r="F43" t="n">
-        <v>1286</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H43" t="b">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1848,15 +1716,12 @@
       <c r="E44" t="n">
         <v>1345</v>
       </c>
-      <c r="F44" t="n">
-        <v>1328</v>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H44" t="b">
+      <c r="G44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1880,15 +1745,12 @@
       <c r="E45" t="n">
         <v>1300</v>
       </c>
-      <c r="F45" t="n">
-        <v>1288</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H45" t="b">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1912,15 +1774,12 @@
       <c r="E46" t="n">
         <v>1460</v>
       </c>
-      <c r="F46" t="n">
-        <v>1456</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H46" t="b">
+      <c r="G46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1944,15 +1803,12 @@
       <c r="E47" t="n">
         <v>1250</v>
       </c>
-      <c r="F47" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H47" t="b">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1976,15 +1832,12 @@
       <c r="E48" t="n">
         <v>1500</v>
       </c>
-      <c r="F48" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H48" t="b">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2008,15 +1861,12 @@
       <c r="E49" t="n">
         <v>1300</v>
       </c>
-      <c r="F49" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H49" t="b">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2040,15 +1890,12 @@
       <c r="E50" t="n">
         <v>1300</v>
       </c>
-      <c r="F50" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H50" t="b">
+      <c r="G50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2072,15 +1919,12 @@
       <c r="E51" t="n">
         <v>1325</v>
       </c>
-      <c r="F51" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H51" t="b">
+      <c r="G51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2104,15 +1948,12 @@
       <c r="E52" t="n">
         <v>1325</v>
       </c>
-      <c r="F52" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H52" t="b">
+      <c r="G52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2136,15 +1977,12 @@
       <c r="E53" t="n">
         <v>1300</v>
       </c>
-      <c r="F53" t="n">
-        <v>1263</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H53" t="b">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G53" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2168,15 +2006,12 @@
       <c r="E54" t="n">
         <v>1400</v>
       </c>
-      <c r="F54" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H54" t="b">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2200,15 +2035,12 @@
       <c r="E55" t="n">
         <v>1500</v>
       </c>
-      <c r="F55" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H55" t="b">
+      <c r="G55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2232,15 +2064,12 @@
       <c r="E56" t="n">
         <v>1275</v>
       </c>
-      <c r="F56" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H56" t="b">
+      <c r="G56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2264,15 +2093,12 @@
       <c r="E57" t="n">
         <v>1225</v>
       </c>
-      <c r="F57" t="n">
-        <v>1213</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H57" t="b">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2296,15 +2122,12 @@
       <c r="E58" t="n">
         <v>1255</v>
       </c>
-      <c r="F58" t="n">
-        <v>1230</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H58" t="b">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2328,15 +2151,12 @@
       <c r="E59" t="n">
         <v>1500</v>
       </c>
-      <c r="F59" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H59" t="b">
+      <c r="G59" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2360,15 +2180,12 @@
       <c r="E60" t="n">
         <v>1250</v>
       </c>
-      <c r="F60" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H60" t="b">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2392,15 +2209,12 @@
       <c r="E61" t="n">
         <v>1300</v>
       </c>
-      <c r="F61" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H61" t="b">
+      <c r="G61" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2424,15 +2238,12 @@
       <c r="E62" t="n">
         <v>1267</v>
       </c>
-      <c r="F62" t="n">
-        <v>1251</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H62" t="b">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G62" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2456,15 +2267,12 @@
       <c r="E63" t="n">
         <v>1267</v>
       </c>
-      <c r="F63" t="n">
-        <v>1251</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H63" t="b">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G63" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2488,15 +2296,12 @@
       <c r="E64" t="n">
         <v>1280</v>
       </c>
-      <c r="F64" t="n">
-        <v>1266</v>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H64" t="b">
+      <c r="G64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2520,15 +2325,12 @@
       <c r="E65" t="n">
         <v>1280</v>
       </c>
-      <c r="F65" t="n">
-        <v>1266</v>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H65" t="b">
+      <c r="G65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2552,15 +2354,12 @@
       <c r="E66" t="n">
         <v>1280</v>
       </c>
-      <c r="F66" t="n">
-        <v>1266</v>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H66" t="b">
+      <c r="G66" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2584,15 +2383,12 @@
       <c r="E67" t="n">
         <v>1200</v>
       </c>
-      <c r="F67" t="n">
-        <v>1176</v>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H67" t="b">
+      <c r="G67" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2616,15 +2412,12 @@
       <c r="E68" t="n">
         <v>1456</v>
       </c>
-      <c r="F68" t="n">
-        <v>1424</v>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H68" t="b">
+      <c r="G68" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2648,15 +2441,12 @@
       <c r="E69" t="n">
         <v>1456</v>
       </c>
-      <c r="F69" t="n">
-        <v>1424</v>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H69" t="b">
+      <c r="G69" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2680,15 +2470,12 @@
       <c r="E70" t="n">
         <v>1456</v>
       </c>
-      <c r="F70" t="n">
-        <v>1424</v>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H70" t="b">
+      <c r="G70" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2712,15 +2499,12 @@
       <c r="E71" t="n">
         <v>1456</v>
       </c>
-      <c r="F71" t="n">
-        <v>1424</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H71" t="b">
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G71" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2744,15 +2528,12 @@
       <c r="E72" t="n">
         <v>1245</v>
       </c>
-      <c r="F72" t="n">
-        <v>1220</v>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H72" t="b">
+      <c r="G72" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2776,15 +2557,12 @@
       <c r="E73" t="n">
         <v>1492</v>
       </c>
-      <c r="F73" t="n">
-        <v>1467</v>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H73" t="b">
+      <c r="G73" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2808,15 +2586,12 @@
       <c r="E74" t="n">
         <v>1492</v>
       </c>
-      <c r="F74" t="n">
-        <v>1490</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H74" t="b">
+      <c r="G74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2840,15 +2615,12 @@
       <c r="E75" t="n">
         <v>1220</v>
       </c>
-      <c r="F75" t="n">
-        <v>1210</v>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H75" t="b">
+      <c r="G75" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2872,15 +2644,12 @@
       <c r="E76" t="n">
         <v>1436</v>
       </c>
-      <c r="F76" t="n">
-        <v>1418</v>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H76" t="b">
+      <c r="G76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2904,15 +2673,12 @@
       <c r="E77" t="n">
         <v>1470</v>
       </c>
-      <c r="F77" t="n">
-        <v>1446</v>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H77" t="b">
+      <c r="G77" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2936,15 +2702,12 @@
       <c r="E78" t="n">
         <v>1200</v>
       </c>
-      <c r="F78" t="n">
-        <v>1190</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H78" t="b">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2968,15 +2731,12 @@
       <c r="E79" t="n">
         <v>1200</v>
       </c>
-      <c r="F79" t="n">
-        <v>1190</v>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H79" t="b">
+      <c r="G79" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3000,15 +2760,12 @@
       <c r="E80" t="n">
         <v>1200</v>
       </c>
-      <c r="F80" t="n">
-        <v>1190</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H80" t="b">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3032,15 +2789,12 @@
       <c r="E81" t="n">
         <v>1200</v>
       </c>
-      <c r="F81" t="n">
-        <v>1190</v>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H81" t="b">
+      <c r="G81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3064,15 +2818,12 @@
       <c r="E82" t="n">
         <v>1230</v>
       </c>
-      <c r="F82" t="n">
-        <v>1220</v>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H82" t="b">
+      <c r="G82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3096,15 +2847,12 @@
       <c r="E83" t="n">
         <v>1290</v>
       </c>
-      <c r="F83" t="n">
-        <v>1288</v>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H83" t="b">
+      <c r="G83" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3128,15 +2876,12 @@
       <c r="E84" t="n">
         <v>1320</v>
       </c>
-      <c r="F84" t="n">
-        <v>1313</v>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H84" t="b">
+      <c r="G84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3160,15 +2905,12 @@
       <c r="E85" t="n">
         <v>1190</v>
       </c>
-      <c r="F85" t="n">
-        <v>1170</v>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H85" t="b">
+      <c r="G85" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3192,15 +2934,12 @@
       <c r="E86" t="n">
         <v>1217</v>
       </c>
-      <c r="F86" t="n">
-        <v>1204</v>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H86" t="b">
+      <c r="G86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3224,15 +2963,12 @@
       <c r="E87" t="n">
         <v>1314</v>
       </c>
-      <c r="F87" t="n">
-        <v>1314</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H87" t="b">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G87" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3256,15 +2992,12 @@
       <c r="E88" t="n">
         <v>1282</v>
       </c>
-      <c r="F88" t="n">
-        <v>1267</v>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H88" t="b">
+      <c r="G88" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3288,15 +3021,12 @@
       <c r="E89" t="n">
         <v>1308</v>
       </c>
-      <c r="F89" t="n">
-        <v>1282</v>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H89" t="b">
+      <c r="G89" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3320,15 +3050,12 @@
       <c r="E90" t="n">
         <v>1308</v>
       </c>
-      <c r="F90" t="n">
-        <v>1282</v>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H90" t="b">
+      <c r="G90" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3352,15 +3079,12 @@
       <c r="E91" t="n">
         <v>1392</v>
       </c>
-      <c r="F91" t="n">
-        <v>1391</v>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H91" t="b">
+      <c r="G91" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3384,15 +3108,12 @@
       <c r="E92" t="n">
         <v>1425</v>
       </c>
-      <c r="F92" t="n">
-        <v>1413</v>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H92" t="b">
+      <c r="G92" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3416,15 +3137,12 @@
       <c r="E93" t="n">
         <v>1300</v>
       </c>
-      <c r="F93" t="n">
-        <v>1276</v>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H93" t="b">
+      <c r="G93" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3448,15 +3166,12 @@
       <c r="E94" t="n">
         <v>1350</v>
       </c>
-      <c r="F94" t="n">
-        <v>1326</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H94" t="b">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G94" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3480,15 +3195,12 @@
       <c r="E95" t="n">
         <v>1172</v>
       </c>
-      <c r="F95" t="n">
-        <v>1172</v>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H95" t="b">
+      <c r="G95" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3512,25 +3224,22 @@
       <c r="E96" t="n">
         <v>1150</v>
       </c>
-      <c r="F96" t="n">
-        <v>1136</v>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H96" t="b">
+      <c r="G96" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>56151</v>
+        <v>56270</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Alexander'</t>
+          <t>'Der Mantel'</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3539,30 +3248,27 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1221</v>
+        <v>1211</v>
       </c>
       <c r="E97" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Rome</t>
-        </is>
-      </c>
-      <c r="H97" t="b">
+        <v>1230</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Britain</t>
+        </is>
+      </c>
+      <c r="G97" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>56153</v>
+        <v>56151</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Barlaam und Josaphat'</t>
+          <t>Rudolf von Ems: 'Alexander'</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3576,25 +3282,22 @@
       <c r="E98" t="n">
         <v>1250</v>
       </c>
-      <c r="F98" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H98" t="b">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="G98" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>56154</v>
+        <v>56153</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Der guote Gêrhart'</t>
+          <t>Rudolf von Ems: 'Barlaam und Josaphat'</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3608,25 +3311,22 @@
       <c r="E99" t="n">
         <v>1250</v>
       </c>
-      <c r="F99" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H99" t="b">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G99" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>56156</v>
+        <v>56154</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Willehalm von Orlens'</t>
+          <t>Rudolf von Ems: 'Der guote Gêrhart'</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3640,25 +3340,22 @@
       <c r="E100" t="n">
         <v>1250</v>
       </c>
-      <c r="F100" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H100" t="b">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G100" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>56159</v>
+        <v>56156</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Seifrit: 'Alexander'</t>
+          <t>Rudolf von Ems: 'Willehalm von Orlens'</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3667,30 +3364,27 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1352</v>
+        <v>1221</v>
       </c>
       <c r="E101" t="n">
-        <v>1352</v>
-      </c>
-      <c r="F101" t="n">
-        <v>1352</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Rome</t>
-        </is>
-      </c>
-      <c r="H101" t="b">
+        <v>1250</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G101" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>56160</v>
+        <v>56159</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sieder, Johann: Übersetzung der 'Alexandervita' mit Vorrede</t>
+          <t>Seifrit: 'Alexander'</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3699,30 +3393,27 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1401</v>
+        <v>1352</v>
       </c>
       <c r="E102" t="n">
-        <v>1502</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1452</v>
-      </c>
-      <c r="G102" t="inlineStr">
+        <v>1352</v>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H102" t="b">
+      <c r="G102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>56162</v>
+        <v>56160</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Steinhöwel, Heinrich: 'Apollonius'</t>
+          <t>Sieder, Johann: Übersetzung der 'Alexandervita' mit Vorrede</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3734,27 +3425,24 @@
         <v>1401</v>
       </c>
       <c r="E103" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1426</v>
-      </c>
-      <c r="G103" t="inlineStr">
+        <v>1502</v>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H103" t="b">
+      <c r="G103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>56164</v>
+        <v>56162</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Stricker: 'Karl der Große'</t>
+          <t>Steinhöwel, Heinrich: 'Apollonius'</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3763,30 +3451,27 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1221</v>
+        <v>1401</v>
       </c>
       <c r="E104" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H104" t="b">
+        <v>1450</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="G104" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>56270</v>
+        <v>56164</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>'Der Mantel'</t>
+          <t>Stricker: 'Karl der Große'</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3795,30 +3480,27 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1211</v>
+        <v>1221</v>
       </c>
       <c r="E105" t="n">
-        <v>1230</v>
-      </c>
-      <c r="F105" t="n">
-        <v>1220</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Britain</t>
-        </is>
-      </c>
-      <c r="H105" t="b">
+        <v>1250</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G105" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>56155</v>
+        <v>56176</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Der guote Gêrhart' (Prosaauflösung)</t>
+          <t>Ulrich von dem Türlin: 'Arabel'</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3827,30 +3509,27 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1221</v>
+        <v>1261</v>
       </c>
       <c r="E106" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H106" t="b">
+        <v>1269</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G106" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>56176</v>
+        <v>56169</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ulrich von dem Türlin: 'Arabel'</t>
+          <t>Ulrich von Etzenbach: 'Alexander'</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3859,30 +3538,27 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="E107" t="n">
-        <v>1269</v>
-      </c>
-      <c r="F107" t="n">
-        <v>1265</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H107" t="b">
+        <v>1297</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="G107" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>56169</v>
+        <v>56170</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Alexander'</t>
+          <t>Ulrich von Etzenbach: 'Alexander-Anhang'</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3896,25 +3572,22 @@
       <c r="E108" t="n">
         <v>1297</v>
       </c>
-      <c r="F108" t="n">
-        <v>1275</v>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H108" t="b">
+      <c r="G108" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>56170</v>
+        <v>56171</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Alexander-Anhang'</t>
+          <t>Ulrich von Etzenbach: 'Wilhelm von Wenden'</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3928,25 +3601,22 @@
       <c r="E109" t="n">
         <v>1297</v>
       </c>
-      <c r="F109" t="n">
-        <v>1275</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Rome</t>
-        </is>
-      </c>
-      <c r="H109" t="b">
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G109" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>56171</v>
+        <v>56173</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Wilhelm von Wenden'</t>
+          <t>Ulrich von Türheim: 'Rennewart'</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3955,30 +3625,27 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1253</v>
+        <v>1226</v>
       </c>
       <c r="E110" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F110" t="n">
         <v>1275</v>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H110" t="b">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G110" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>56173</v>
+        <v>56175</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Rennewart'</t>
+          <t>Ulrich von Türheim: 'Tristan'</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3987,30 +3654,27 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="E111" t="n">
-        <v>1275</v>
-      </c>
-      <c r="F111" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H111" t="b">
+        <v>1243</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Britain</t>
+        </is>
+      </c>
+      <c r="G111" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>56175</v>
+        <v>56177</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Tristan'</t>
+          <t>Ulrich von Zatzikhoven: 'Lanzelet'</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4019,30 +3683,27 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1231</v>
+        <v>1176</v>
       </c>
       <c r="E112" t="n">
-        <v>1243</v>
-      </c>
-      <c r="F112" t="n">
-        <v>1237</v>
-      </c>
-      <c r="G112" t="inlineStr">
+        <v>1225</v>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H112" t="b">
+      <c r="G112" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>56177</v>
+        <v>56187</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ulrich von Zatzikhoven: 'Lanzelet'</t>
+          <t>Wirnt von Grafenberg: 'Wigalois'</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4051,30 +3712,27 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1176</v>
+        <v>1204</v>
       </c>
       <c r="E113" t="n">
-        <v>1225</v>
-      </c>
-      <c r="F113" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G113" t="inlineStr">
+        <v>1230</v>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H113" t="b">
+      <c r="G113" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>56187</v>
+        <v>56189</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wirnt von Grafenberg: 'Wigalois'</t>
+          <t>Wolfram von Eschenbach: 'Parzival'</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4083,30 +3741,27 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="E114" t="n">
-        <v>1230</v>
-      </c>
-      <c r="F114" t="n">
-        <v>1217</v>
-      </c>
-      <c r="G114" t="inlineStr">
+        <v>1210</v>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H114" t="b">
+      <c r="G114" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>56189</v>
+        <v>56190</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Parzival'</t>
+          <t>Wolfram von Eschenbach: 'Titurel'</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4115,30 +3770,27 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="E115" t="n">
-        <v>1210</v>
-      </c>
-      <c r="F115" t="n">
-        <v>1206</v>
-      </c>
-      <c r="G115" t="inlineStr">
+        <v>1250</v>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H115" t="b">
+      <c r="G115" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>56190</v>
+        <v>56191</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Titurel'</t>
+          <t>Wolfram von Eschenbach: 'Willehalm'</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4147,30 +3799,27 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="E116" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F116" t="n">
-        <v>1234</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Britain</t>
-        </is>
-      </c>
-      <c r="H116" t="b">
+        <v>1220</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G116" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>56191</v>
+        <v>56140</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Willehalm'</t>
+          <t>'Abor und das Meerweib'</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4179,30 +3828,27 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1211</v>
+        <v>1301</v>
       </c>
       <c r="E117" t="n">
-        <v>1220</v>
-      </c>
-      <c r="F117" t="n">
-        <v>1216</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H117" t="b">
+        <v>1350</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Britain</t>
+        </is>
+      </c>
+      <c r="G117" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>56140</v>
+        <v>56199</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>'Abor und das Meerweib'</t>
+          <t>'Ainune'</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4211,30 +3857,27 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1301</v>
+        <v>1201</v>
       </c>
       <c r="E118" t="n">
-        <v>1350</v>
-      </c>
-      <c r="F118" t="n">
-        <v>1326</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Britain</t>
-        </is>
-      </c>
-      <c r="H118" t="b">
+        <v>1250</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G118" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>56199</v>
+        <v>56232</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>'Ainune'</t>
+          <t>'Alischanz'</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4246,27 +3889,24 @@
         <v>1201</v>
       </c>
       <c r="E119" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F119" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H119" t="b">
+        <v>1300</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G119" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>56232</v>
+        <v>56254</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>'Alischanz'</t>
+          <t>'Athis und Prophilias'</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4275,30 +3915,27 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1201</v>
+        <v>1101</v>
       </c>
       <c r="E120" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F120" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H120" t="b">
+        <v>1200</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G120" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>56254</v>
+        <v>56198</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>'Athis und Prophilias'</t>
+          <t>'Dietrich und Fasold'</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4307,30 +3944,27 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1101</v>
+        <v>1201</v>
       </c>
       <c r="E121" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F121" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H121" t="b">
-        <v>0</v>
+        <v>1300</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G121" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>56198</v>
+        <v>56200</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>'Dietrich und Fasold'</t>
+          <t>'Dietrich und Wenezlan'</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4342,27 +3976,24 @@
         <v>1201</v>
       </c>
       <c r="E122" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F122" t="n">
         <v>1250</v>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H122" t="b">
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G122" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>56200</v>
+        <v>56203</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>'Dietrich und Wenezlan'</t>
+          <t>'Edolanz'</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4371,30 +4002,27 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1201</v>
+        <v>1226</v>
       </c>
       <c r="E123" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F123" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H123" t="b">
-        <v>1</v>
+        <v>1275</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Britain</t>
+        </is>
+      </c>
+      <c r="G123" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>56203</v>
+        <v>56218</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>'Edolanz'</t>
+          <t>'Graf Rudolf'</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4403,30 +4031,27 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1226</v>
+        <v>1171</v>
       </c>
       <c r="E124" t="n">
-        <v>1275</v>
-      </c>
-      <c r="F124" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Britain</t>
-        </is>
-      </c>
-      <c r="H124" t="b">
+        <v>1173</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G124" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>56218</v>
+        <v>56236</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>'Graf Rudolf'</t>
+          <t>'Herzog Ernst' A</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4435,30 +4060,27 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1171</v>
+        <v>1101</v>
       </c>
       <c r="E125" t="n">
-        <v>1173</v>
-      </c>
-      <c r="F125" t="n">
-        <v>1172</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H125" t="b">
+        <v>1200</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G125" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>56236</v>
+        <v>56241</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' A</t>
+          <t>'Herzog Ernst' Kl</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4467,30 +4089,27 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1101</v>
+        <v>1301</v>
       </c>
       <c r="E126" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F126" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H126" t="b">
+        <v>1400</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G126" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>56241</v>
+        <v>56245</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' Kl</t>
+          <t>'Hürnen Seyfrid'</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4499,30 +4118,27 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1301</v>
+        <v>1401</v>
       </c>
       <c r="E127" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F127" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H127" t="b">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G127" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>56245</v>
+        <v>56250</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>'Hürnen Seyfrid'</t>
+          <t>'Karl und Galie'</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4531,30 +4147,27 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1401</v>
+        <v>1216</v>
       </c>
       <c r="E128" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F128" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H128" t="b">
-        <v>1</v>
+        <v>1220</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>56250</v>
+        <v>56264</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>'Karl und Galie'</t>
+          <t>'Linzer Oswald'</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4563,30 +4176,27 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1216</v>
+        <v>1301</v>
       </c>
       <c r="E129" t="n">
-        <v>1220</v>
-      </c>
-      <c r="F129" t="n">
-        <v>1218</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H129" t="b">
+        <v>1350</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G129" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>56264</v>
+        <v>56271</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>'Linzer Oswald'</t>
+          <t>'Manuel und Amande'</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4595,30 +4205,27 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1301</v>
+        <v>1276</v>
       </c>
       <c r="E130" t="n">
-        <v>1350</v>
-      </c>
-      <c r="F130" t="n">
-        <v>1326</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="H130" t="b">
+        <v>1300</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Britain</t>
+        </is>
+      </c>
+      <c r="G130" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>56271</v>
+        <v>56272</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>'Manuel und Amande'</t>
+          <t>'Mitteldeutscher Erec'</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4627,30 +4234,27 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1276</v>
+        <v>1201</v>
       </c>
       <c r="E131" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F131" t="n">
-        <v>1288</v>
-      </c>
-      <c r="G131" t="inlineStr">
+        <v>1250</v>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H131" t="b">
+      <c r="G131" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>56272</v>
+        <v>56278</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>'Mitteldeutscher Erec'</t>
+          <t>'Niederfränkischer Tristan'</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4662,27 +4266,24 @@
         <v>1201</v>
       </c>
       <c r="E132" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F132" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G132" t="inlineStr">
+        <v>1300</v>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H132" t="b">
+      <c r="G132" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>56278</v>
+        <v>56282</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>'Niederfränkischer Tristan'</t>
+          <t>'Ospinel'</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4694,27 +4295,24 @@
         <v>1201</v>
       </c>
       <c r="E133" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F133" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Britain</t>
-        </is>
-      </c>
-      <c r="H133" t="b">
+        <v>1225</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G133" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>56282</v>
+        <v>56286</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>'Ospinel'</t>
+          <t>'Parcheval'</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4726,27 +4324,24 @@
         <v>1201</v>
       </c>
       <c r="E134" t="n">
-        <v>1225</v>
-      </c>
-      <c r="F134" t="n">
-        <v>1213</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H134" t="b">
+        <v>1250</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Britain</t>
+        </is>
+      </c>
+      <c r="G134" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>56286</v>
+        <v>56158</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>'Parcheval'</t>
+          <t>'Segremors'</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4755,30 +4350,27 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1201</v>
+        <v>1251</v>
       </c>
       <c r="E135" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F135" t="n">
-        <v>1226</v>
-      </c>
-      <c r="G135" t="inlineStr">
+        <v>1270</v>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Britain</t>
         </is>
       </c>
-      <c r="H135" t="b">
+      <c r="G135" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>56158</v>
+        <v>56165</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>'Segremors'</t>
+          <t>'Trierer Floyris'</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4787,30 +4379,27 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1251</v>
+        <v>1146</v>
       </c>
       <c r="E136" t="n">
-        <v>1270</v>
-      </c>
-      <c r="F136" t="n">
-        <v>1260</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Britain</t>
-        </is>
-      </c>
-      <c r="H136" t="b">
+        <v>1195</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="G136" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>56165</v>
+        <v>56180</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>'Trierer Floyris'</t>
+          <t>'Waldecker (Marburger) Alexander'</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4819,30 +4408,27 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1146</v>
+        <v>1101</v>
       </c>
       <c r="E137" t="n">
-        <v>1195</v>
-      </c>
-      <c r="F137" t="n">
-        <v>1170</v>
-      </c>
-      <c r="G137" t="inlineStr">
+        <v>1500</v>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>Rome</t>
         </is>
       </c>
-      <c r="H137" t="b">
+      <c r="G137" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>56180</v>
+        <v>56181</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>'Waldecker (Marburger) Alexander'</t>
+          <t>'Walther und Hildegund'</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4851,30 +4437,27 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1101</v>
+        <v>1201</v>
       </c>
       <c r="E138" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F138" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Rome</t>
-        </is>
-      </c>
-      <c r="H138" t="b">
-        <v>0</v>
+        <v>1275</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G138" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>56181</v>
+        <v>56141</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>'Walther und Hildegund'</t>
+          <t>Berthold von Holle: 'Darifant'</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4883,30 +4466,27 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1201</v>
+        <v>1235</v>
       </c>
       <c r="E139" t="n">
-        <v>1275</v>
-      </c>
-      <c r="F139" t="n">
-        <v>1238</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H139" t="b">
-        <v>1</v>
+        <v>1267</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G139" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>56141</v>
+        <v>56197</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Darifant'</t>
+          <t>Dietrich von Hopfgarten: 'Wigelis'</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4915,30 +4495,27 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1235</v>
+        <v>1221</v>
       </c>
       <c r="E140" t="n">
-        <v>1267</v>
-      </c>
-      <c r="F140" t="n">
-        <v>1251</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H140" t="b">
+        <v>1455</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Britain</t>
+        </is>
+      </c>
+      <c r="G140" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>56197</v>
+        <v>56223</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dietrich von Hopfgarten: 'Wigelis'</t>
+          <t>Hans von Bühel: 'Die Königstochter von Frankreich'</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4947,30 +4524,27 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1221</v>
+        <v>1400</v>
       </c>
       <c r="E141" t="n">
-        <v>1455</v>
-      </c>
-      <c r="F141" t="n">
-        <v>1338</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Britain</t>
-        </is>
-      </c>
-      <c r="H141" t="b">
+        <v>1400</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G141" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>56223</v>
+        <v>56172</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Hans von Bühel: 'Die Königstochter von Frankreich'</t>
+          <t>Ulrich von Türheim: 'Kliges'</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4979,30 +4553,27 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1400</v>
+        <v>1231</v>
       </c>
       <c r="E142" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F142" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H142" t="b">
+        <v>1240</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="G142" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>56172</v>
+        <v>56155</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Kliges'</t>
+          <t>Rudolf von Ems: 'Der guote Gêrhart' (Prosaauflösung)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5011,20 +4582,17 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="E143" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F143" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Rome</t>
-        </is>
-      </c>
-      <c r="H143" t="b">
+        <v>1250</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G143" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5048,15 +4616,12 @@
       <c r="E144" t="n">
         <v>1200</v>
       </c>
-      <c r="F144" t="n">
-        <v>1188</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="H144" t="b">
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G144" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/german_works.xlsx
+++ b/data/german_works.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G57" t="b">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G71" t="b">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G101" t="b">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G106" t="b">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G110" t="b">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G116" t="b">

--- a/data/german_works.xlsx
+++ b/data/german_works.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,6 +428,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +464,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>matiere_source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>is_heldenepik</t>
         </is>
       </c>
@@ -503,7 +498,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G2" t="b">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -532,7 +532,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G3" t="b">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -561,7 +566,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G4" t="b">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -590,7 +600,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G5" t="b">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -619,7 +634,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G6" t="b">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -648,7 +668,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G7" t="b">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -677,7 +702,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G8" t="b">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -706,7 +736,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G9" t="b">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -735,7 +770,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G10" t="b">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -764,7 +804,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G11" t="b">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -793,7 +838,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G12" t="b">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -822,7 +872,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G13" t="b">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -851,7 +906,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G14" t="b">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -880,7 +940,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G15" t="b">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -909,7 +974,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G16" t="b">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -938,7 +1008,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G17" t="b">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -967,7 +1042,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G18" t="b">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -996,7 +1076,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G19" t="b">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1025,7 +1110,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G20" t="b">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1054,7 +1144,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G21" t="b">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1083,7 +1178,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G22" t="b">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1112,7 +1212,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G23" t="b">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1141,7 +1246,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G24" t="b">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1170,7 +1280,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G25" t="b">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1199,7 +1314,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G26" t="b">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1228,7 +1348,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G27" t="b">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1257,7 +1382,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G28" t="b">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1286,7 +1416,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G29" t="b">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1315,7 +1450,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G30" t="b">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1344,7 +1484,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G31" t="b">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H31" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1373,7 +1518,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G32" t="b">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1402,7 +1552,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G33" t="b">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1431,7 +1586,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G34" t="b">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1460,7 +1620,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G35" t="b">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1489,7 +1654,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G36" t="b">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1518,7 +1688,12 @@
           <t>England</t>
         </is>
       </c>
-      <c r="G37" t="b">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1547,7 +1722,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G38" t="b">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1576,7 +1756,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G39" t="b">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1605,7 +1790,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G40" t="b">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1634,7 +1824,12 @@
           <t>England</t>
         </is>
       </c>
-      <c r="G41" t="b">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1663,7 +1858,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G42" t="b">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1692,7 +1892,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G43" t="b">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1721,7 +1926,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G44" t="b">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1750,7 +1960,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G45" t="b">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1779,7 +1994,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G46" t="b">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1808,7 +2028,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G47" t="b">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H47" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1837,7 +2062,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G48" t="b">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1866,7 +2096,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G49" t="b">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1895,7 +2130,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G50" t="b">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1924,7 +2164,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G51" t="b">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1953,7 +2198,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G52" t="b">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1982,7 +2232,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G53" t="b">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H53" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2011,7 +2266,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G54" t="b">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2040,7 +2300,12 @@
           <t>England</t>
         </is>
       </c>
-      <c r="G55" t="b">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2069,7 +2334,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G56" t="b">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2098,7 +2368,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G57" t="b">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="H57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2127,7 +2402,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G58" t="b">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2156,7 +2436,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G59" t="b">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H59" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2185,7 +2470,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G60" t="b">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2214,7 +2504,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G61" t="b">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H61" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2243,7 +2538,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G62" t="b">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H62" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2272,7 +2572,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G63" t="b">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H63" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2301,7 +2606,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G64" t="b">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2330,7 +2640,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G65" t="b">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2359,7 +2674,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G66" t="b">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H66" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2388,7 +2708,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G67" t="b">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H67" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2417,7 +2742,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G68" t="b">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H68" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2446,7 +2776,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G69" t="b">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H69" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2475,7 +2810,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G70" t="b">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H70" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2504,7 +2844,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G71" t="b">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="H71" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2533,7 +2878,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G72" t="b">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H72" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2562,7 +2912,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G73" t="b">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H73" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2591,7 +2946,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G74" t="b">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2620,7 +2980,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G75" t="b">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H75" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2649,7 +3014,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G76" t="b">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2678,7 +3048,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G77" t="b">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H77" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2707,7 +3082,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G78" t="b">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2736,7 +3116,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G79" t="b">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H79" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2765,7 +3150,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G80" t="b">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2794,7 +3184,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G81" t="b">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2823,7 +3218,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G82" t="b">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2852,7 +3252,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G83" t="b">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H83" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2881,7 +3286,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G84" t="b">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2910,7 +3320,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G85" t="b">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H85" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2939,7 +3354,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G86" t="b">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2968,7 +3388,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G87" t="b">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H87" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2997,7 +3422,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G88" t="b">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H88" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3026,7 +3456,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G89" t="b">
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H89" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3055,7 +3490,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G90" t="b">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H90" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3084,7 +3524,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G91" t="b">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H91" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3113,7 +3558,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G92" t="b">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H92" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3142,7 +3592,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G93" t="b">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H93" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3171,7 +3626,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G94" t="b">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H94" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3200,7 +3660,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G95" t="b">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H95" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3229,7 +3694,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G96" t="b">
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H96" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3258,7 +3728,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G97" t="b">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H97" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3287,7 +3762,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G98" t="b">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H98" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3316,7 +3796,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G99" t="b">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H99" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3345,7 +3830,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G100" t="b">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H100" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3374,7 +3864,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G101" t="b">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="H101" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3403,7 +3898,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G102" t="b">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H102" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3432,7 +3932,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G103" t="b">
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H103" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3461,7 +3966,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G104" t="b">
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H104" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3490,7 +4000,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G105" t="b">
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H105" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3519,7 +4034,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G106" t="b">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="H106" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3548,7 +4068,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G107" t="b">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H107" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3577,7 +4102,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G108" t="b">
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H108" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3606,7 +4136,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G109" t="b">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H109" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3635,7 +4170,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G110" t="b">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="H110" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3664,7 +4204,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G111" t="b">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H111" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3693,7 +4238,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G112" t="b">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H112" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3722,7 +4272,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G113" t="b">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H113" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3751,7 +4306,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G114" t="b">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H114" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3780,7 +4340,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G115" t="b">
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H115" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3809,7 +4374,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G116" t="b">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="H116" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3838,7 +4408,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G117" t="b">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H117" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3867,7 +4442,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G118" t="b">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H118" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3896,7 +4476,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G119" t="b">
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H119" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3925,7 +4510,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G120" t="b">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H120" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3954,7 +4544,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G121" t="b">
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H121" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3983,7 +4578,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G122" t="b">
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H122" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4012,7 +4612,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G123" t="b">
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H123" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4041,7 +4646,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G124" t="b">
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H124" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4070,7 +4680,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G125" t="b">
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H125" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4099,7 +4714,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G126" t="b">
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H126" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4128,7 +4748,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G127" t="b">
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H127" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4157,7 +4782,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G128" t="b">
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H128" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4186,7 +4816,12 @@
           <t>England</t>
         </is>
       </c>
-      <c r="G129" t="b">
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H129" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4215,7 +4850,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G130" t="b">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H130" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4244,7 +4884,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G131" t="b">
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H131" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4273,7 +4918,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G132" t="b">
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H132" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4302,7 +4952,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="G133" t="b">
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H133" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4331,7 +4986,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G134" t="b">
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H134" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4360,7 +5020,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G135" t="b">
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H135" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4389,7 +5054,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G136" t="b">
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H136" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4418,7 +5088,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G137" t="b">
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H137" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4447,7 +5122,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G138" t="b">
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H138" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4476,7 +5156,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G139" t="b">
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H139" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4505,7 +5190,12 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="G140" t="b">
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H140" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4534,7 +5224,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G141" t="b">
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H141" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4563,7 +5258,12 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="G142" t="b">
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>storyverse</t>
+        </is>
+      </c>
+      <c r="H142" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4592,7 +5292,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G143" t="b">
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H143" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4621,7 +5326,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G144" t="b">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="H144" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/german_works.xlsx
+++ b/data/german_works.xlsx
@@ -1685,7 +1685,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">

--- a/data/german_works.xlsx
+++ b/data/german_works.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>'Alpharts Tod'</t>
+          <t>Alpharts Tod</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>'Bairisch-österreichisches Buch von Troja' (früher: 'Buch von Troja II')</t>
+          <t>Bairisch-österreichisches Buch von Troja' (früher: 'Buch von Troja II')</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>'Biterolf und Dietleib' ('Biterolf')</t>
+          <t>Biterolf und Dietleib' ('Biterolf')</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'Breslauer Apollonius'</t>
+          <t>Breslauer Apollonius</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'Buch von Troja nach Guido de Columnis'</t>
+          <t>Buch von Troja nach Guido de Columnis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'Cleomades'</t>
+          <t>Cleomades</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'Daniel'</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'Der Große Alexander'</t>
+          <t>Der Große Alexander</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'Der Wunderer'</t>
+          <t>Der Wunderer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'Die gute Frau'</t>
+          <t>Die gute Frau</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>'Die Königin vom Brennenden See'</t>
+          <t>Die Königin vom Brennenden See</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>'Dietrichs Flucht'</t>
+          <t>Dietrichs Flucht</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>'Eckenlied'</t>
+          <t>Eckenlied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>'Elsässisches Trojabuch'</t>
+          <t>Elsässisches Trojabuch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>'Friedrich von Schwaben'</t>
+          <t>Friedrich von Schwaben</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>'Göttweiger Trojanerkrieg'</t>
+          <t>Göttweiger Trojanerkrieg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' B</t>
+          <t>Herzog Ernst' B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' D</t>
+          <t>Herzog Ernst' D</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' F</t>
+          <t>Herzog Ernst' F</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' G</t>
+          <t>Herzog Ernst' G</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>'Hildebrandslied'</t>
+          <t>Hildebrandslied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>'Historie van Sent Reinolt'</t>
+          <t>Historie van Sent Reinolt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>'Johann aus dem Virgiere'</t>
+          <t>Johann aus dem Virgiere</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>'Jüngeres Hildebrandslied'</t>
+          <t>Jüngeres Hildebrandslied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>'Karl und Elegast'</t>
+          <t>Karl und Elegast</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>'Karlmeinet'-Kompilation</t>
+          <t>Karlmeinet'-Kompilation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>'König Rother'</t>
+          <t>König Rother</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>'Kudrun'</t>
+          <t>Kudrun</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>'Lancelot'</t>
+          <t>Lancelot</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>'Laurin'</t>
+          <t>Laurin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>'Leipziger Apollonius'</t>
+          <t>Leipziger Apollonius</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>'Lohengrin'</t>
+          <t>Lohengrin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>'Mai und Beaflor'</t>
+          <t>Mai und Beaflor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>'Malagis'</t>
+          <t>Malagis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>'Morant und Galie'</t>
+          <t>Morant und Galie</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>'Münchner Oswald'</t>
+          <t>Münchner Oswald</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'Nibelungenlied'</t>
+          <t>Nibelungenlied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>'Ogier von Dänemark'</t>
+          <t>Ogier von Dänemark</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>'Ortnit'</t>
+          <t>Ortnit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>'Oswald' / 'Berliner Oswald'</t>
+          <t>Oswald' / 'Berliner Oswald</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>'Pontus und Sidonia'</t>
+          <t>Pontus und Sidonia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>'Rabenschlacht'</t>
+          <t>Rabenschlacht</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>'Rappoltsteiner Parzifal'</t>
+          <t>Rappoltsteiner Parzifal</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>'Reinfried von Braunschweig'</t>
+          <t>Reinfried von Braunschweig</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>'Reinolt von Montelban'</t>
+          <t>Reinolt von Montelban</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>'Rosengarten zu Worms'</t>
+          <t>Rosengarten zu Worms</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>'Salman und Morolf'</t>
+          <t>Salman und Morolf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>'Sigenot'</t>
+          <t>Sigenot</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>'Tristan als Mönch'</t>
+          <t>Tristan als Mönch</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>'Trojanerkrieg'</t>
+          <t>Trojanerkrieg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>'Trojanerkrieg'-Fortsetzung</t>
+          <t>Trojanerkrieg'-Fortsetzung</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>'Virginal'</t>
+          <t>Virginal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>'Walberan'</t>
+          <t>Walberan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>'Wiener Oswald'</t>
+          <t>Wiener Oswald</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>'Wigamur'</t>
+          <t>Wigamur</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>'Willehalm' (Prosaroman)</t>
+          <t>Willehalm' (Prosaroman)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>'Wolfdietrich'</t>
+          <t>Wolfdietrich</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>'Zürcher Buch vom heiligen Karl'</t>
+          <t>Zürcher Buch vom heiligen Karl</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Albrecht von Kemenaten: 'Goldemar'</t>
+          <t>Albrecht von Kemenaten: 'Goldemar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Albrecht: 'Jüngerer Titurel'</t>
+          <t>Albrecht: 'Jüngerer Titurel</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Crane'</t>
+          <t>Berthold von Holle: 'Crane</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Demantin'</t>
+          <t>Berthold von Holle: 'Demantin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Der Pleier: 'Garel von dem blühenden Tal'</t>
+          <t>Der Pleier: 'Garel von dem blühenden Tal</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Der Pleier: 'Meleranz'</t>
+          <t>Der Pleier: 'Meleranz</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Der Pleier: 'Tandareis und Flordibel'</t>
+          <t>Der Pleier: 'Tandareis und Flordibel</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eilhart von Oberg: 'Tristrant'</t>
+          <t>Eilhart von Oberg: 'Tristrant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Herpin'</t>
+          <t>Elisabeth von Nassau-Saarbrücken: 'Herpin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Huge Scheppel'</t>
+          <t>Elisabeth von Nassau-Saarbrücken: 'Huge Scheppel</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Loher und Maller'</t>
+          <t>Elisabeth von Nassau-Saarbrücken: 'Loher und Maller</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Sibille'</t>
+          <t>Elisabeth von Nassau-Saarbrücken: 'Sibille</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fleck, Konrad: 'Flore und Blanscheflur'</t>
+          <t>Fleck, Konrad: 'Flore und Blanscheflur</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gottfried von Straßburg: 'Tristan'</t>
+          <t>Gottfried von Straßburg: 'Tristan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gutevrunt, Heinrich: 'Historia von der vorstorunge troye'</t>
+          <t>Gutevrunt, Heinrich: 'Historia von der vorstorunge troye</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hartlieb, Johannes: 'Alexander'</t>
+          <t>Hartlieb, Johannes: 'Alexander</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Der arme Heinrich'</t>
+          <t>Hartmann von Aue: 'Der arme Heinrich</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Erec'</t>
+          <t>Hartmann von Aue: 'Erec</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Gregorius'</t>
+          <t>Hartmann von Aue: 'Gregorius</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Iwein'</t>
+          <t>Hartmann von Aue: 'Iwein</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Heinrich von dem Türlin: 'Diu Crône'</t>
+          <t>Heinrich von dem Türlin: 'Diu Crône</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Heinrich von Freiberg: 'Tristan'</t>
+          <t>Heinrich von Freiberg: 'Tristan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Heinrich von Neustadt: 'Apollonius von Tyrland'</t>
+          <t>Heinrich von Neustadt: 'Apollonius von Tyrland</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Heinrich von Veldeke: 'Eneas'</t>
+          <t>Heinrich von Veldeke: 'Eneas</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Herbort von Fritzlar: 'Liet von Troye'</t>
+          <t>Herbort von Fritzlar: 'Liet von Troye</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Johann von Würzburg: 'Wilhelm von Österreich'</t>
+          <t>Johann von Würzburg: 'Wilhelm von Österreich</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Konrad von Stoffeln: 'Gauriel von Muntabel'</t>
+          <t>Konrad von Stoffeln: 'Gauriel von Muntabel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Konrad von Würzburg: 'Partonopier und Meliur'</t>
+          <t>Konrad von Würzburg: 'Partonopier und Meliur</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Konrad von Würzburg: 'Trojanerkrieg'</t>
+          <t>Konrad von Würzburg: 'Trojanerkrieg</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mair, Hans, von Nördlingen: 'Buch von Troja'</t>
+          <t>Mair, Hans, von Nördlingen: 'Buch von Troja</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Meister Wichwolt [früher: Babiloth]: 'Cronica Allexandri des grossen konigs'</t>
+          <t>Meister Wichwolt [früher: Babiloth]: 'Cronica Allexandri des grossen konigs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Otte: 'Eraclius'</t>
+          <t>Otte: 'Eraclius</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Otto II. von Freising: 'Barlaam und Josaphat'</t>
+          <t>Otto II. von Freising: 'Barlaam und Josaphat</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pfaffe Konrad: 'Rolandslied'</t>
+          <t>Pfaffe Konrad: 'Rolandslied</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pfaffe Lambrecht: 'Alexanderlied'</t>
+          <t>Pfaffe Lambrecht: 'Alexanderlied</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>'Der Mantel'</t>
+          <t>Der Mantel</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Alexander'</t>
+          <t>Rudolf von Ems: 'Alexander</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Barlaam und Josaphat'</t>
+          <t>Rudolf von Ems: 'Barlaam und Josaphat</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Der guote Gêrhart'</t>
+          <t>Rudolf von Ems: 'Der guote Gêrhart</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Willehalm von Orlens'</t>
+          <t>Rudolf von Ems: 'Willehalm von Orlens</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Seifrit: 'Alexander'</t>
+          <t>Seifrit: 'Alexander</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Steinhöwel, Heinrich: 'Apollonius'</t>
+          <t>Steinhöwel, Heinrich: 'Apollonius</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Stricker: 'Karl der Große'</t>
+          <t>Stricker: 'Karl der Große</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ulrich von dem Türlin: 'Arabel'</t>
+          <t>Ulrich von dem Türlin: 'Arabel</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Alexander'</t>
+          <t>Ulrich von Etzenbach: 'Alexander</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Alexander-Anhang'</t>
+          <t>Ulrich von Etzenbach: 'Alexander-Anhang</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Wilhelm von Wenden'</t>
+          <t>Ulrich von Etzenbach: 'Wilhelm von Wenden</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Rennewart'</t>
+          <t>Ulrich von Türheim: 'Rennewart</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Tristan'</t>
+          <t>Ulrich von Türheim: 'Tristan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ulrich von Zatzikhoven: 'Lanzelet'</t>
+          <t>Ulrich von Zatzikhoven: 'Lanzelet</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Wirnt von Grafenberg: 'Wigalois'</t>
+          <t>Wirnt von Grafenberg: 'Wigalois</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Parzival'</t>
+          <t>Wolfram von Eschenbach: 'Parzival</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Titurel'</t>
+          <t>Wolfram von Eschenbach: 'Titurel</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Willehalm'</t>
+          <t>Wolfram von Eschenbach: 'Willehalm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>'Abor und das Meerweib'</t>
+          <t>Abor und das Meerweib</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>'Ainune'</t>
+          <t>Ainune</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>'Alischanz'</t>
+          <t>Alischanz</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>'Athis und Prophilias'</t>
+          <t>Athis und Prophilias</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>'Dietrich und Fasold'</t>
+          <t>Dietrich und Fasold</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>'Dietrich und Wenezlan'</t>
+          <t>Dietrich und Wenezlan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>'Edolanz'</t>
+          <t>Edolanz</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>'Graf Rudolf'</t>
+          <t>Graf Rudolf</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' A</t>
+          <t>Herzog Ernst' A</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' Kl</t>
+          <t>Herzog Ernst' Kl</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>'Hürnen Seyfrid'</t>
+          <t>Hürnen Seyfrid</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>'Karl und Galie'</t>
+          <t>Karl und Galie</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>'Linzer Oswald'</t>
+          <t>Linzer Oswald</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>'Manuel und Amande'</t>
+          <t>Manuel und Amande</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>'Mitteldeutscher Erec'</t>
+          <t>Mitteldeutscher Erec</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>'Niederfränkischer Tristan'</t>
+          <t>Niederfränkischer Tristan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>'Ospinel'</t>
+          <t>Ospinel</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>'Parcheval'</t>
+          <t>Parcheval</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>'Segremors'</t>
+          <t>Segremors</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>'Trierer Floyris'</t>
+          <t>Trierer Floyris</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>'Waldecker (Marburger) Alexander'</t>
+          <t>Waldecker (Marburger) Alexander</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>'Walther und Hildegund'</t>
+          <t>Walther und Hildegund</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Darifant'</t>
+          <t>Berthold von Holle: 'Darifant</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dietrich von Hopfgarten: 'Wigelis'</t>
+          <t>Dietrich von Hopfgarten: 'Wigelis</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Hans von Bühel: 'Die Königstochter von Frankreich'</t>
+          <t>Hans von Bühel: 'Die Königstochter von Frankreich</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Kliges'</t>
+          <t>Ulrich von Türheim: 'Kliges</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>'Orendel' ('Der Graue Rock')</t>
+          <t>Orendel' ('Der Graue Rock')</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">

--- a/data/german_works.xlsx
+++ b/data/german_works.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H2" t="b">

--- a/data/german_works.xlsx
+++ b/data/german_works.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,13 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3861,12 +3872,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H101" t="b">

--- a/data/german_works.xlsx
+++ b/data/german_works.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,8 +427,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/data/german_works.xlsx
+++ b/data/german_works.xlsx
@@ -475,11 +475,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56243</v>
+        <v>56140</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alpharts Tod</t>
+          <t>Abor und das Meerweib</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -488,32 +488,32 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1251</v>
+        <v>1301</v>
       </c>
       <c r="E2" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56265</v>
+        <v>56199</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bairisch-österreichisches Buch von Troja' (früher: 'Buch von Troja II')</t>
+          <t>Ainune</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1301</v>
+        <v>1201</v>
       </c>
       <c r="E3" t="n">
-        <v>1400</v>
+        <v>1250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -543,11 +543,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56163</v>
+        <v>56232</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Biterolf und Dietleib' ('Biterolf')</t>
+          <t>Alischanz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,32 +556,32 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1251</v>
+        <v>1201</v>
       </c>
       <c r="E4" t="n">
-        <v>1260</v>
+        <v>1300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56174</v>
+        <v>56254</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Breslauer Apollonius</t>
+          <t>Athis und Prophilias</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -590,14 +590,14 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1401</v>
+        <v>1101</v>
       </c>
       <c r="E5" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -611,11 +611,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56185</v>
+        <v>56265</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Buch von Troja nach Guido de Columnis</t>
+          <t>Bairisch-österreichisches Buch von Troja (früher: Buch von Troja II)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1401</v>
+        <v>1301</v>
       </c>
       <c r="E6" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -645,11 +645,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56195</v>
+        <v>56185</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cleomades</t>
+          <t>Buch von Troja nach Guido de Columnis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1426</v>
+        <v>1401</v>
       </c>
       <c r="E7" t="n">
-        <v>1475</v>
+        <v>1500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -679,11 +679,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56196</v>
+        <v>56220</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Die gute Frau</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,14 +692,14 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1221</v>
+        <v>1206</v>
       </c>
       <c r="E8" t="n">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -713,11 +713,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56219</v>
+        <v>56198</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Der Große Alexander</t>
+          <t>Dietrich und Fasold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -726,32 +726,32 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1301</v>
+        <v>1201</v>
       </c>
       <c r="E9" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56192</v>
+        <v>56200</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Der Wunderer</t>
+          <t>Dietrich und Wenezlan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -763,7 +763,7 @@
         <v>1201</v>
       </c>
       <c r="E10" t="n">
-        <v>1472</v>
+        <v>1250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -781,11 +781,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56220</v>
+        <v>56201</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Die gute Frau</t>
+          <t>Dietrichs Flucht</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1206</v>
+        <v>1101</v>
       </c>
       <c r="E11" t="n">
-        <v>1255</v>
+        <v>1300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -810,16 +810,16 @@
         </is>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>56253</v>
+        <v>56202</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Die Königin vom Brennenden See</t>
+          <t>Eckenlied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1351</v>
+        <v>1201</v>
       </c>
       <c r="E12" t="n">
-        <v>1474</v>
+        <v>1250</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56201</v>
+        <v>56203</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dietrichs Flucht</t>
+          <t>Edolanz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -862,14 +862,14 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1101</v>
+        <v>1226</v>
       </c>
       <c r="E13" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -878,16 +878,16 @@
         </is>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>56202</v>
+        <v>56209</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eckenlied</t>
+          <t>Elsässisches Trojabuch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -896,32 +896,32 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1201</v>
+        <v>1376</v>
       </c>
       <c r="E14" t="n">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>56209</v>
+        <v>56218</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Elsässisches Trojabuch</t>
+          <t>Graf Rudolf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -930,19 +930,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1376</v>
+        <v>1171</v>
       </c>
       <c r="E15" t="n">
-        <v>1400</v>
+        <v>1173</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -951,11 +951,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>56213</v>
+        <v>56236</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Friedrich von Schwaben</t>
+          <t>Herzog Ernst A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1314</v>
+        <v>1101</v>
       </c>
       <c r="E16" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -985,11 +985,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>56217</v>
+        <v>56237</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Göttweiger Trojanerkrieg</t>
+          <t>Herzog Ernst B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -998,19 +998,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1271</v>
+        <v>1201</v>
       </c>
       <c r="E17" t="n">
         <v>1300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1019,11 +1019,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>56237</v>
+        <v>56238</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Herzog Ernst' B</t>
+          <t>Herzog Ernst D</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1053,11 +1053,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>56238</v>
+        <v>56240</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Herzog Ernst' D</t>
+          <t>Herzog Ernst G</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1201</v>
+        <v>1301</v>
       </c>
       <c r="E19" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1087,11 +1087,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>56239</v>
+        <v>56241</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Herzog Ernst' F</t>
+          <t>Herzog Ernst Kl</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1401</v>
+        <v>1301</v>
       </c>
       <c r="E20" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1121,11 +1121,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>56240</v>
+        <v>56245</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Herzog Ernst' G</t>
+          <t>Hürnen Seyfrid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1301</v>
+        <v>1401</v>
       </c>
       <c r="E21" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>56242</v>
+        <v>56248</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hildebrandslied</t>
+          <t>Jüngeres Hildebrandslied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>701</v>
+        <v>1251</v>
       </c>
       <c r="E22" t="n">
-        <v>840</v>
+        <v>1350</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1189,11 +1189,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>56244</v>
+        <v>56250</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Historie van Sent Reinolt</t>
+          <t>Karl und Galie</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1401</v>
+        <v>1216</v>
       </c>
       <c r="E23" t="n">
-        <v>1450</v>
+        <v>1220</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1223,11 +1223,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>56246</v>
+        <v>56252</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Johann aus dem Virgiere</t>
+          <t>König Rother</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1351</v>
+        <v>1101</v>
       </c>
       <c r="E24" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1257,11 +1257,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>56248</v>
+        <v>56261</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jüngeres Hildebrandslied</t>
+          <t>Lancelot</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1270,32 +1270,32 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1251</v>
+        <v>1201</v>
       </c>
       <c r="E25" t="n">
-        <v>1350</v>
+        <v>1250</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>56249</v>
+        <v>56262</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Karl und Elegast</t>
+          <t>Laurin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1304,32 +1304,32 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1301</v>
+        <v>1201</v>
       </c>
       <c r="E26" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56251</v>
+        <v>56264</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Karlmeinet'-Kompilation</t>
+          <t>Linzer Oswald</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1359,11 +1359,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>56252</v>
+        <v>56266</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>König Rother</t>
+          <t>Lohengrin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1101</v>
+        <v>1283</v>
       </c>
       <c r="E28" t="n">
-        <v>1200</v>
+        <v>1289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1393,11 +1393,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>56259</v>
+        <v>56271</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kudrun</t>
+          <t>Manuel und Amande</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1406,14 +1406,14 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1201</v>
+        <v>1276</v>
       </c>
       <c r="E29" t="n">
         <v>1300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1422,16 +1422,16 @@
         </is>
       </c>
       <c r="H29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>56261</v>
+        <v>56272</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lancelot</t>
+          <t>Mitteldeutscher Erec</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1461,11 +1461,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>56262</v>
+        <v>56273</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Laurin</t>
+          <t>Morant und Galie</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1477,11 +1477,11 @@
         <v>1201</v>
       </c>
       <c r="E31" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="H31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>56263</v>
+        <v>56277</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Leipziger Apollonius</t>
+          <t>Nibelungenlied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1508,14 +1508,14 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1300</v>
+        <v>1181</v>
       </c>
       <c r="E32" t="n">
-        <v>1450</v>
+        <v>1210</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1524,16 +1524,16 @@
         </is>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>56266</v>
+        <v>56278</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lohengrin</t>
+          <t>Niederfränkischer Tristan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1542,19 +1542,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1283</v>
+        <v>1201</v>
       </c>
       <c r="E33" t="n">
-        <v>1289</v>
+        <v>1300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -1563,11 +1563,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>56267</v>
+        <v>56281</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mai und Beaflor</t>
+          <t>Ortnit</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1271</v>
+        <v>1206</v>
       </c>
       <c r="E34" t="n">
-        <v>1280</v>
+        <v>1255</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>56269</v>
+        <v>56282</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Malagis</t>
+          <t>Ospinel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1451</v>
+        <v>1201</v>
       </c>
       <c r="E35" t="n">
-        <v>1460</v>
+        <v>1225</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -1631,11 +1631,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56273</v>
+        <v>56286</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Morant und Galie</t>
+          <t>Parcheval</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1647,16 +1647,16 @@
         <v>1201</v>
       </c>
       <c r="E36" t="n">
-        <v>1230</v>
+        <v>1250</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -1665,11 +1665,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56274</v>
+        <v>56146</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Münchner Oswald</t>
+          <t>Rabenschlacht</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1401</v>
+        <v>1276</v>
       </c>
       <c r="E37" t="n">
-        <v>1450</v>
+        <v>1296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1694,16 +1694,16 @@
         </is>
       </c>
       <c r="H37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>56277</v>
+        <v>56150</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nibelungenlied</t>
+          <t>Rosengarten zu Worms</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1181</v>
+        <v>1201</v>
       </c>
       <c r="E38" t="n">
-        <v>1210</v>
+        <v>1250</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1733,11 +1733,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>56279</v>
+        <v>56157</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ogier von Dänemark</t>
+          <t>Salman und Morolf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1746,19 +1746,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1451</v>
+        <v>1400</v>
       </c>
       <c r="E39" t="n">
         <v>1500</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -1767,11 +1767,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>56281</v>
+        <v>56158</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ortnit</t>
+          <t>Segremors</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1780,14 +1780,14 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1206</v>
+        <v>1251</v>
       </c>
       <c r="E40" t="n">
-        <v>1255</v>
+        <v>1270</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1796,16 +1796,16 @@
         </is>
       </c>
       <c r="H40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>56283</v>
+        <v>56161</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Oswald' / 'Berliner Oswald</t>
+          <t>Sigenot</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1401</v>
+        <v>1201</v>
       </c>
       <c r="E41" t="n">
-        <v>1475</v>
+        <v>1300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>56145</v>
+        <v>56165</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pontus und Sidonia</t>
+          <t>Trierer Floyris</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1848,19 +1848,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1401</v>
+        <v>1146</v>
       </c>
       <c r="E42" t="n">
-        <v>1500</v>
+        <v>1195</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H42" t="b">
@@ -1869,11 +1869,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>56146</v>
+        <v>56178</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rabenschlacht</t>
+          <t>Virginal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1276</v>
+        <v>1226</v>
       </c>
       <c r="E43" t="n">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1903,11 +1903,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>56147</v>
+        <v>56179</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rappoltsteiner Parzifal</t>
+          <t>Walberan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1916,32 +1916,32 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1311</v>
+        <v>1201</v>
       </c>
       <c r="E44" t="n">
-        <v>1345</v>
+        <v>1400</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>56148</v>
+        <v>56180</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Reinfried von Braunschweig</t>
+          <t>Waldecker (Marburger) Alexander</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1950,19 +1950,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1276</v>
+        <v>1101</v>
       </c>
       <c r="E45" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H45" t="b">
@@ -1971,11 +1971,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>56149</v>
+        <v>56181</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Reinolt von Montelban</t>
+          <t>Walther und Hildegund</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1984,32 +1984,32 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1451</v>
+        <v>1201</v>
       </c>
       <c r="E46" t="n">
-        <v>1460</v>
+        <v>1275</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>56150</v>
+        <v>56184</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rosengarten zu Worms</t>
+          <t>Wigamur</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2018,14 +2018,14 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1201</v>
+        <v>1226</v>
       </c>
       <c r="E47" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="H47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>56157</v>
+        <v>56188</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Salman und Morolf</t>
+          <t>Wolfdietrich</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1400</v>
+        <v>1206</v>
       </c>
       <c r="E48" t="n">
-        <v>1500</v>
+        <v>1255</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2068,16 +2068,16 @@
         </is>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>56161</v>
+        <v>56210</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sigenot</t>
+          <t>Albrecht: Jüngerer Titurel</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="H49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>56166</v>
+        <v>56276</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tristan als Mönch</t>
+          <t>Berthold von Holle: Crane</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2120,19 +2120,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1201</v>
+        <v>1235</v>
       </c>
       <c r="E50" t="n">
-        <v>1300</v>
+        <v>1267</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H50" t="b">
@@ -2141,11 +2141,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>56167</v>
+        <v>56141</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trojanerkrieg</t>
+          <t>Berthold von Holle: Darifant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2154,19 +2154,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1276</v>
+        <v>1235</v>
       </c>
       <c r="E51" t="n">
-        <v>1325</v>
+        <v>1267</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H51" t="b">
@@ -2175,11 +2175,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>56168</v>
+        <v>56152</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trojanerkrieg'-Fortsetzung</t>
+          <t>Berthold von Holle: Demantin</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2188,19 +2188,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1276</v>
+        <v>1235</v>
       </c>
       <c r="E52" t="n">
-        <v>1325</v>
+        <v>1267</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H52" t="b">
@@ -2209,11 +2209,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>56178</v>
+        <v>56142</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Virginal</t>
+          <t>Der Pleier: Garel von dem blühenden Tal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2222,14 +2222,14 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1226</v>
+        <v>1251</v>
       </c>
       <c r="E53" t="n">
-        <v>1300</v>
+        <v>1280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="H53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>56179</v>
+        <v>56144</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Walberan</t>
+          <t>Der Pleier: Tandareis und Flordibel</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2256,14 +2256,14 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1201</v>
+        <v>1251</v>
       </c>
       <c r="E54" t="n">
-        <v>1400</v>
+        <v>1280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2272,16 +2272,16 @@
         </is>
       </c>
       <c r="H54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>56183</v>
+        <v>56197</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wiener Oswald</t>
+          <t>Dietrich von Hopfgarten: Wigelis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2290,14 +2290,14 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1401</v>
+        <v>1221</v>
       </c>
       <c r="E55" t="n">
-        <v>1500</v>
+        <v>1455</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2311,11 +2311,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>56184</v>
+        <v>56204</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wigamur</t>
+          <t>Eilhart von Oberg: Tristrant</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1226</v>
+        <v>1151</v>
       </c>
       <c r="E56" t="n">
-        <v>1275</v>
+        <v>1200</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H56" t="b">
@@ -2345,11 +2345,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56186</v>
+        <v>56212</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Willehalm' (Prosaroman)</t>
+          <t>Fleck, Konrad: Flore und Blanscheflur</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2358,19 +2358,19 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="E57" t="n">
-        <v>1225</v>
+        <v>1245</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H57" t="b">
@@ -2379,11 +2379,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>56188</v>
+        <v>56215</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wolfdietrich</t>
+          <t>Fuetrer, Ulrich: Lanzelot (strophisch) (Buch der Abenteuer III)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2392,32 +2392,32 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1206</v>
+        <v>1487</v>
       </c>
       <c r="E58" t="n">
-        <v>1255</v>
+        <v>1492</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>56193</v>
+        <v>56216</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zürcher Buch vom heiligen Karl</t>
+          <t>Gottfried von Straßburg: Tristan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2426,14 +2426,14 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1401</v>
+        <v>1201</v>
       </c>
       <c r="E59" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2447,11 +2447,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>56221</v>
+        <v>56222</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Albrecht von Kemenaten: 'Goldemar</t>
+          <t>Gutevrunt, Heinrich: Historia von der vorstorunge troye</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2460,32 +2460,32 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1201</v>
+        <v>1401</v>
       </c>
       <c r="E60" t="n">
-        <v>1250</v>
+        <v>1436</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>56210</v>
+        <v>56223</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Albrecht: 'Jüngerer Titurel</t>
+          <t>Hans von Bühel: Die Königstochter von Frankreich</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2494,14 +2494,14 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1201</v>
+        <v>1400</v>
       </c>
       <c r="E61" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2515,11 +2515,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>56276</v>
+        <v>56225</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Crane</t>
+          <t>Hartmann von Aue: Der arme Heinrich</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1235</v>
+        <v>1181</v>
       </c>
       <c r="E62" t="n">
-        <v>1267</v>
+        <v>1200</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2549,11 +2549,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>56152</v>
+        <v>56226</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Demantin</t>
+          <t>Hartmann von Aue: Erec</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2562,19 +2562,19 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1235</v>
+        <v>1181</v>
       </c>
       <c r="E63" t="n">
-        <v>1267</v>
+        <v>1200</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H63" t="b">
@@ -2583,11 +2583,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>56142</v>
+        <v>56227</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Der Pleier: 'Garel von dem blühenden Tal</t>
+          <t>Hartmann von Aue: Gregorius</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2596,14 +2596,14 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1251</v>
+        <v>1181</v>
       </c>
       <c r="E64" t="n">
-        <v>1280</v>
+        <v>1200</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2617,11 +2617,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>56143</v>
+        <v>56228</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Der Pleier: 'Meleranz</t>
+          <t>Hartmann von Aue: Iwein</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1251</v>
+        <v>1181</v>
       </c>
       <c r="E65" t="n">
-        <v>1280</v>
+        <v>1200</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H65" t="b">
@@ -2651,11 +2651,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>56144</v>
+        <v>56233</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Der Pleier: 'Tandareis und Flordibel</t>
+          <t>Heinrich von dem Türlin: Diu Crône</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1251</v>
+        <v>1211</v>
       </c>
       <c r="E66" t="n">
-        <v>1280</v>
+        <v>1230</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2685,11 +2685,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>56204</v>
+        <v>56229</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eilhart von Oberg: 'Tristrant</t>
+          <t>Heinrich von Freiberg: Tristan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1151</v>
+        <v>1286</v>
       </c>
       <c r="E67" t="n">
-        <v>1200</v>
+        <v>1290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2719,11 +2719,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>56205</v>
+        <v>56230</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Herpin</t>
+          <t>Heinrich von Neustadt: Apollonius von Tyrland</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2732,19 +2732,19 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1393</v>
+        <v>1306</v>
       </c>
       <c r="E68" t="n">
-        <v>1456</v>
+        <v>1320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H68" t="b">
@@ -2753,11 +2753,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>56206</v>
+        <v>56234</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Huge Scheppel</t>
+          <t>Heinrich von Veldeke: Eneas</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2766,14 +2766,14 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1393</v>
+        <v>1151</v>
       </c>
       <c r="E69" t="n">
-        <v>1456</v>
+        <v>1190</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2787,11 +2787,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>56207</v>
+        <v>56235</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Loher und Maller</t>
+          <t>Herbort von Fritzlar: Liet von Troye</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2800,14 +2800,14 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1393</v>
+        <v>1191</v>
       </c>
       <c r="E70" t="n">
-        <v>1456</v>
+        <v>1217</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2821,11 +2821,11 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>56208</v>
+        <v>56247</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Sibille</t>
+          <t>Johann von Würzburg: Wilhelm von Österreich</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2834,19 +2834,19 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1393</v>
+        <v>1314</v>
       </c>
       <c r="E71" t="n">
-        <v>1456</v>
+        <v>1314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H71" t="b">
@@ -2855,11 +2855,11 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>56212</v>
+        <v>56256</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fleck, Konrad: 'Flore und Blanscheflur</t>
+          <t>Konrad von Stoffeln: Gauriel von Muntabel</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1196</v>
+        <v>1252</v>
       </c>
       <c r="E72" t="n">
-        <v>1245</v>
+        <v>1282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H72" t="b">
@@ -2889,11 +2889,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>56214</v>
+        <v>56257</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fuetrer, Ulrich: 'Lanzelot' (Prosaroman)</t>
+          <t>Konrad von Würzburg: Partonopier und Meliur</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2902,14 +2902,14 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1442</v>
+        <v>1257</v>
       </c>
       <c r="E73" t="n">
-        <v>1492</v>
+        <v>1308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2923,11 +2923,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>56215</v>
+        <v>56258</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fuetrer, Ulrich: 'Lanzelot' (strophisch) ('Buch der Abenteuer' III)</t>
+          <t>Konrad von Würzburg: Trojanerkrieg</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2936,14 +2936,14 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1487</v>
+        <v>1257</v>
       </c>
       <c r="E74" t="n">
-        <v>1492</v>
+        <v>1308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2957,11 +2957,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>56216</v>
+        <v>56255</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gottfried von Straßburg: 'Tristan</t>
+          <t>Pfaffe Konrad: Rolandslied</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2970,14 +2970,14 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1201</v>
+        <v>1172</v>
       </c>
       <c r="E75" t="n">
-        <v>1220</v>
+        <v>1172</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2991,11 +2991,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>56222</v>
+        <v>56151</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gutevrunt, Heinrich: 'Historia von der vorstorunge troye</t>
+          <t>Rudolf von Ems: Alexander</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1401</v>
+        <v>1221</v>
       </c>
       <c r="E76" t="n">
-        <v>1436</v>
+        <v>1250</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3025,11 +3025,11 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>56224</v>
+        <v>56153</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hartlieb, Johannes: 'Alexander</t>
+          <t>Rudolf von Ems: Barlaam und Josaphat</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3038,19 +3038,19 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1421</v>
+        <v>1221</v>
       </c>
       <c r="E77" t="n">
-        <v>1470</v>
+        <v>1250</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H77" t="b">
@@ -3059,11 +3059,11 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>56225</v>
+        <v>56156</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Der arme Heinrich</t>
+          <t>Rudolf von Ems: Willehalm von Orlens</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1181</v>
+        <v>1221</v>
       </c>
       <c r="E78" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3093,11 +3093,11 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>56226</v>
+        <v>56164</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Erec</t>
+          <t>Stricker: Karl der Große</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3106,14 +3106,14 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1181</v>
+        <v>1221</v>
       </c>
       <c r="E79" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3127,11 +3127,11 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>56227</v>
+        <v>56176</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Gregorius</t>
+          <t>Ulrich von dem Türlin: Arabel</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3140,19 +3140,19 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1181</v>
+        <v>1261</v>
       </c>
       <c r="E80" t="n">
-        <v>1200</v>
+        <v>1269</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>override</t>
         </is>
       </c>
       <c r="H80" t="b">
@@ -3161,11 +3161,11 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>56228</v>
+        <v>56169</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Iwein</t>
+          <t>Ulrich von Etzenbach: Alexander</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3174,14 +3174,14 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1181</v>
+        <v>1253</v>
       </c>
       <c r="E81" t="n">
-        <v>1200</v>
+        <v>1297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3195,11 +3195,11 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>56233</v>
+        <v>56172</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Heinrich von dem Türlin: 'Diu Crône</t>
+          <t>Ulrich von Türheim: Kliges</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3208,19 +3208,19 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1211</v>
+        <v>1231</v>
       </c>
       <c r="E82" t="n">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H82" t="b">
@@ -3229,11 +3229,11 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>56229</v>
+        <v>56173</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Heinrich von Freiberg: 'Tristan</t>
+          <t>Ulrich von Türheim: Rennewart</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3242,19 +3242,19 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1286</v>
+        <v>1226</v>
       </c>
       <c r="E83" t="n">
-        <v>1290</v>
+        <v>1275</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
       <c r="H83" t="b">
@@ -3263,11 +3263,11 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>56230</v>
+        <v>56177</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Heinrich von Neustadt: 'Apollonius von Tyrland</t>
+          <t>Ulrich von Zatzikhoven: Lanzelet</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3276,19 +3276,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1306</v>
+        <v>1176</v>
       </c>
       <c r="E84" t="n">
-        <v>1320</v>
+        <v>1225</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H84" t="b">
@@ -3297,11 +3297,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>56234</v>
+        <v>56187</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Heinrich von Veldeke: 'Eneas</t>
+          <t>Wirnt von Grafenberg: Wigalois</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3310,19 +3310,19 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1151</v>
+        <v>1204</v>
       </c>
       <c r="E85" t="n">
-        <v>1190</v>
+        <v>1230</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H85" t="b">
@@ -3331,11 +3331,11 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>56235</v>
+        <v>56189</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Herbort von Fritzlar: 'Liet von Troye</t>
+          <t>Wolfram von Eschenbach: Parzival</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3344,14 +3344,14 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1191</v>
+        <v>1201</v>
       </c>
       <c r="E86" t="n">
-        <v>1217</v>
+        <v>1210</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3365,11 +3365,11 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>56247</v>
+        <v>56155</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Johann von Würzburg: 'Wilhelm von Österreich</t>
+          <t>Rudolf von Ems: Der guote Gêrhart (Prosaauflösung)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1314</v>
+        <v>1221</v>
       </c>
       <c r="E87" t="n">
-        <v>1314</v>
+        <v>1250</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3399,11 +3399,11 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>56256</v>
+        <v>56190</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Konrad von Stoffeln: 'Gauriel von Muntabel</t>
+          <t>Wolfram von Eschenbach: Titurel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1252</v>
+        <v>1217</v>
       </c>
       <c r="E88" t="n">
-        <v>1282</v>
+        <v>1250</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3433,11 +3433,11 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>56257</v>
+        <v>56191</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Konrad von Würzburg: 'Partonopier und Meliur</t>
+          <t>Wolfram von Eschenbach: Willehalm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3446,19 +3446,19 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1257</v>
+        <v>1211</v>
       </c>
       <c r="E89" t="n">
-        <v>1308</v>
+        <v>1220</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>override</t>
         </is>
       </c>
       <c r="H89" t="b">
@@ -3467,11 +3467,11 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>56258</v>
+        <v>56196</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Konrad von Würzburg: 'Trojanerkrieg</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3480,19 +3480,19 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1257</v>
+        <v>1221</v>
       </c>
       <c r="E90" t="n">
-        <v>1308</v>
+        <v>1250</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H90" t="b">
@@ -3501,11 +3501,11 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>56268</v>
+        <v>56280</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mair, Hans, von Nördlingen: 'Buch von Troja</t>
+          <t>Orendel (Der Graue Rock)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3514,19 +3514,19 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1390</v>
+        <v>1176</v>
       </c>
       <c r="E91" t="n">
-        <v>1392</v>
+        <v>1200</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H91" t="b">
@@ -3535,11 +3535,11 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>56182</v>
+        <v>56168</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Meister Wichwolt [früher: Babiloth]: 'Cronica Allexandri des grossen konigs</t>
+          <t>Trojanerkrieg-Fortsetzung</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1401</v>
+        <v>1276</v>
       </c>
       <c r="E92" t="n">
-        <v>1425</v>
+        <v>1325</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3569,11 +3569,11 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>56284</v>
+        <v>56260</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Otte: 'Eraclius</t>
+          <t>Pfaffe Lambrecht: Alexanderlied</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1251</v>
+        <v>1121</v>
       </c>
       <c r="E93" t="n">
-        <v>1300</v>
+        <v>1150</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3603,11 +3603,11 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>56285</v>
+        <v>56243</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Otto II. von Freising: 'Barlaam und Josaphat</t>
+          <t>Alpharts Tod</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1301</v>
+        <v>1251</v>
       </c>
       <c r="E94" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3632,16 +3632,16 @@
         </is>
       </c>
       <c r="H94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>56255</v>
+        <v>56163</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pfaffe Konrad: 'Rolandslied</t>
+          <t>Biterolf und Dietleib (Biterolf)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3650,32 +3650,32 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1172</v>
+        <v>1251</v>
       </c>
       <c r="E95" t="n">
-        <v>1172</v>
+        <v>1260</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>56260</v>
+        <v>56174</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pfaffe Lambrecht: 'Alexanderlied</t>
+          <t>Breslauer Apollonius</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1121</v>
+        <v>1401</v>
       </c>
       <c r="E96" t="n">
-        <v>1150</v>
+        <v>1500</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H96" t="b">
@@ -3705,11 +3705,11 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>56270</v>
+        <v>56195</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Der Mantel</t>
+          <t>Cleomades</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3718,14 +3718,14 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1211</v>
+        <v>1426</v>
       </c>
       <c r="E97" t="n">
-        <v>1230</v>
+        <v>1475</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3739,11 +3739,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>56151</v>
+        <v>56219</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Alexander</t>
+          <t>Der Große Alexander</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1221</v>
+        <v>1301</v>
       </c>
       <c r="E98" t="n">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3773,11 +3773,11 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>56153</v>
+        <v>56192</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Barlaam und Josaphat</t>
+          <t>Der Wunderer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1221</v>
+        <v>1201</v>
       </c>
       <c r="E99" t="n">
-        <v>1250</v>
+        <v>1472</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3802,16 +3802,16 @@
         </is>
       </c>
       <c r="H99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>56154</v>
+        <v>56253</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Der guote Gêrhart</t>
+          <t>Die Königin vom Brennenden See</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1221</v>
+        <v>1351</v>
       </c>
       <c r="E100" t="n">
-        <v>1250</v>
+        <v>1474</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3841,11 +3841,11 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>56156</v>
+        <v>56213</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Willehalm von Orlens</t>
+          <t>Friedrich von Schwaben</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1221</v>
+        <v>1314</v>
       </c>
       <c r="E101" t="n">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3875,11 +3875,11 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>56159</v>
+        <v>56217</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Seifrit: 'Alexander</t>
+          <t>Göttweiger Trojanerkrieg</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1352</v>
+        <v>1271</v>
       </c>
       <c r="E102" t="n">
-        <v>1352</v>
+        <v>1300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3909,11 +3909,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>56160</v>
+        <v>56239</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sieder, Johann: Übersetzung der 'Alexandervita' mit Vorrede</t>
+          <t>Herzog Ernst F</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3925,16 +3925,16 @@
         <v>1401</v>
       </c>
       <c r="E103" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H103" t="b">
@@ -3943,11 +3943,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>56162</v>
+        <v>56242</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Steinhöwel, Heinrich: 'Apollonius</t>
+          <t>Hildebrandslied</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3956,14 +3956,14 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1401</v>
+        <v>701</v>
       </c>
       <c r="E104" t="n">
-        <v>1450</v>
+        <v>840</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3972,16 +3972,16 @@
         </is>
       </c>
       <c r="H104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>56164</v>
+        <v>56244</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Stricker: 'Karl der Große</t>
+          <t>Historie van Sent Reinolt</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1221</v>
+        <v>1401</v>
       </c>
       <c r="E105" t="n">
-        <v>1250</v>
+        <v>1450</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4011,11 +4011,11 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>56176</v>
+        <v>56246</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ulrich von dem Türlin: 'Arabel</t>
+          <t>Johann aus dem Virgiere</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4024,19 +4024,19 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1261</v>
+        <v>1351</v>
       </c>
       <c r="E106" t="n">
-        <v>1269</v>
+        <v>1400</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H106" t="b">
@@ -4045,11 +4045,11 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>56169</v>
+        <v>56249</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Alexander</t>
+          <t>Karl und Elegast</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4058,14 +4058,14 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1253</v>
+        <v>1301</v>
       </c>
       <c r="E107" t="n">
-        <v>1297</v>
+        <v>1400</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4079,11 +4079,11 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>56170</v>
+        <v>56251</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Alexander-Anhang</t>
+          <t>Karlmeinet-Kompilation</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4092,14 +4092,14 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1253</v>
+        <v>1301</v>
       </c>
       <c r="E108" t="n">
-        <v>1297</v>
+        <v>1350</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4113,11 +4113,11 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>56171</v>
+        <v>56259</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Wilhelm von Wenden</t>
+          <t>Kudrun</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1253</v>
+        <v>1201</v>
       </c>
       <c r="E109" t="n">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4142,16 +4142,16 @@
         </is>
       </c>
       <c r="H109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>56173</v>
+        <v>56263</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Rennewart</t>
+          <t>Leipziger Apollonius</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4160,19 +4160,19 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1226</v>
+        <v>1300</v>
       </c>
       <c r="E110" t="n">
-        <v>1275</v>
+        <v>1450</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H110" t="b">
@@ -4181,11 +4181,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>56175</v>
+        <v>56267</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Tristan</t>
+          <t>Mai und Beaflor</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4194,19 +4194,19 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1231</v>
+        <v>1271</v>
       </c>
       <c r="E111" t="n">
-        <v>1243</v>
+        <v>1280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H111" t="b">
@@ -4215,11 +4215,11 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>56177</v>
+        <v>56269</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ulrich von Zatzikhoven: 'Lanzelet</t>
+          <t>Malagis</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4228,14 +4228,14 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1176</v>
+        <v>1451</v>
       </c>
       <c r="E112" t="n">
-        <v>1225</v>
+        <v>1460</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4249,11 +4249,11 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>56187</v>
+        <v>56274</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Wirnt von Grafenberg: 'Wigalois</t>
+          <t>Münchner Oswald</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4262,14 +4262,14 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1204</v>
+        <v>1401</v>
       </c>
       <c r="E113" t="n">
-        <v>1230</v>
+        <v>1450</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4283,11 +4283,11 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>56189</v>
+        <v>56279</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Parzival</t>
+          <t>Ogier von Dänemark</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4296,14 +4296,14 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1201</v>
+        <v>1451</v>
       </c>
       <c r="E114" t="n">
-        <v>1210</v>
+        <v>1500</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4317,11 +4317,11 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>56190</v>
+        <v>56283</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Titurel</t>
+          <t>Oswald / Berliner Oswald</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4330,14 +4330,14 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1217</v>
+        <v>1401</v>
       </c>
       <c r="E115" t="n">
-        <v>1250</v>
+        <v>1475</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4351,11 +4351,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>56191</v>
+        <v>56145</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Willehalm</t>
+          <t>Pontus und Sidonia</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4364,19 +4364,19 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1211</v>
+        <v>1401</v>
       </c>
       <c r="E116" t="n">
-        <v>1220</v>
+        <v>1500</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H116" t="b">
@@ -4385,11 +4385,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>56140</v>
+        <v>56147</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Abor und das Meerweib</t>
+          <t>Rappoltsteiner Parzifal</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1301</v>
+        <v>1311</v>
       </c>
       <c r="E117" t="n">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -4419,11 +4419,11 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>56199</v>
+        <v>56148</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ainune</t>
+          <t>Reinfried von Braunschweig</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1201</v>
+        <v>1276</v>
       </c>
       <c r="E118" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -4453,11 +4453,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>56232</v>
+        <v>56149</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Alischanz</t>
+          <t>Reinolt von Montelban</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4466,10 +4466,10 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1201</v>
+        <v>1451</v>
       </c>
       <c r="E119" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4487,11 +4487,11 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>56254</v>
+        <v>56166</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Athis und Prophilias</t>
+          <t>Tristan als Mönch</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4500,19 +4500,19 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1101</v>
+        <v>1201</v>
       </c>
       <c r="E120" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H120" t="b">
@@ -4521,11 +4521,11 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>56198</v>
+        <v>56167</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dietrich und Fasold</t>
+          <t>Trojanerkrieg</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4534,32 +4534,32 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1201</v>
+        <v>1276</v>
       </c>
       <c r="E121" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>56200</v>
+        <v>56183</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dietrich und Wenezlan</t>
+          <t>Wiener Oswald</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1201</v>
+        <v>1401</v>
       </c>
       <c r="E122" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -4584,16 +4584,16 @@
         </is>
       </c>
       <c r="H122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>56203</v>
+        <v>56186</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Edolanz</t>
+          <t>Willehalm (Prosaroman)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1226</v>
+        <v>1201</v>
       </c>
       <c r="E123" t="n">
-        <v>1275</v>
+        <v>1225</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>override</t>
         </is>
       </c>
       <c r="H123" t="b">
@@ -4623,11 +4623,11 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>56218</v>
+        <v>56193</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Graf Rudolf</t>
+          <t>Zürcher Buch vom heiligen Karl</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4636,19 +4636,19 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1171</v>
+        <v>1401</v>
       </c>
       <c r="E124" t="n">
-        <v>1173</v>
+        <v>1500</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H124" t="b">
@@ -4657,11 +4657,11 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>56236</v>
+        <v>56221</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Herzog Ernst' A</t>
+          <t>Albrecht von Kemenaten: Goldemar</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4670,10 +4670,10 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1101</v>
+        <v>1201</v>
       </c>
       <c r="E125" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         </is>
       </c>
       <c r="H125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>56241</v>
+        <v>56143</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Herzog Ernst' Kl</t>
+          <t>Der Pleier: Meleranz</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4704,14 +4704,14 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1301</v>
+        <v>1251</v>
       </c>
       <c r="E126" t="n">
-        <v>1400</v>
+        <v>1280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4725,11 +4725,11 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>56245</v>
+        <v>56205</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Hürnen Seyfrid</t>
+          <t>Elisabeth von Nassau-Saarbrücken: Herpin</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4738,32 +4738,32 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1401</v>
+        <v>1393</v>
       </c>
       <c r="E127" t="n">
-        <v>1500</v>
+        <v>1456</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>56250</v>
+        <v>56206</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Karl und Galie</t>
+          <t>Elisabeth von Nassau-Saarbrücken: Huge Scheppel</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1216</v>
+        <v>1393</v>
       </c>
       <c r="E128" t="n">
-        <v>1220</v>
+        <v>1456</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4793,11 +4793,11 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>56264</v>
+        <v>56207</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Linzer Oswald</t>
+          <t>Elisabeth von Nassau-Saarbrücken: Loher und Maller</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4806,19 +4806,19 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1301</v>
+        <v>1393</v>
       </c>
       <c r="E129" t="n">
-        <v>1350</v>
+        <v>1456</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H129" t="b">
@@ -4827,11 +4827,11 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>56271</v>
+        <v>56208</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Manuel und Amande</t>
+          <t>Elisabeth von Nassau-Saarbrücken: Sibille</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4840,19 +4840,19 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1276</v>
+        <v>1393</v>
       </c>
       <c r="E130" t="n">
-        <v>1300</v>
+        <v>1456</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>override</t>
         </is>
       </c>
       <c r="H130" t="b">
@@ -4861,11 +4861,11 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>56272</v>
+        <v>56214</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mitteldeutscher Erec</t>
+          <t>Fuetrer, Ulrich: Lanzelot (Prosaroman)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1201</v>
+        <v>1442</v>
       </c>
       <c r="E131" t="n">
-        <v>1250</v>
+        <v>1492</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4895,11 +4895,11 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>56278</v>
+        <v>56224</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Niederfränkischer Tristan</t>
+          <t>Hartlieb, Johannes: Alexander</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4908,14 +4908,14 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1201</v>
+        <v>1421</v>
       </c>
       <c r="E132" t="n">
-        <v>1300</v>
+        <v>1470</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4929,11 +4929,11 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>56282</v>
+        <v>56268</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ospinel</t>
+          <t>Mair, Hans, von Nördlingen: Buch von Troja</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4942,19 +4942,19 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1201</v>
+        <v>1390</v>
       </c>
       <c r="E133" t="n">
-        <v>1225</v>
+        <v>1392</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H133" t="b">
@@ -4963,11 +4963,11 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>56286</v>
+        <v>56182</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Parcheval</t>
+          <t>Meister Wichwolt [früher: Babiloth]: Cronica Allexandri des grossen konigs</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4976,14 +4976,14 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1201</v>
+        <v>1401</v>
       </c>
       <c r="E134" t="n">
-        <v>1250</v>
+        <v>1425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -4997,11 +4997,11 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>56158</v>
+        <v>56284</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Segremors</t>
+          <t>Otte: Eraclius</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5013,16 +5013,16 @@
         <v>1251</v>
       </c>
       <c r="E135" t="n">
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H135" t="b">
@@ -5031,11 +5031,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>56165</v>
+        <v>56285</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Trierer Floyris</t>
+          <t>Otto II. von Freising: Barlaam und Josaphat</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5044,19 +5044,19 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1146</v>
+        <v>1301</v>
       </c>
       <c r="E136" t="n">
-        <v>1195</v>
+        <v>1350</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H136" t="b">
@@ -5065,11 +5065,11 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>56180</v>
+        <v>56270</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Waldecker (Marburger) Alexander</t>
+          <t>Der Mantel</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5078,19 +5078,19 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1101</v>
+        <v>1211</v>
       </c>
       <c r="E137" t="n">
-        <v>1500</v>
+        <v>1230</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>storyverse</t>
+          <t>local</t>
         </is>
       </c>
       <c r="H137" t="b">
@@ -5099,11 +5099,11 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>56181</v>
+        <v>56154</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Walther und Hildegund</t>
+          <t>Rudolf von Ems: Der guote Gêrhart</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1201</v>
+        <v>1221</v>
       </c>
       <c r="E138" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -5128,16 +5128,16 @@
         </is>
       </c>
       <c r="H138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>56141</v>
+        <v>56159</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Darifant</t>
+          <t>Seifrit: Alexander</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5146,19 +5146,19 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1235</v>
+        <v>1352</v>
       </c>
       <c r="E139" t="n">
-        <v>1267</v>
+        <v>1352</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H139" t="b">
@@ -5167,11 +5167,11 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>56197</v>
+        <v>56160</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dietrich von Hopfgarten: 'Wigelis</t>
+          <t>Sieder, Johann: Übersetzung der Alexandervita mit Vorrede</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5180,19 +5180,19 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1221</v>
+        <v>1401</v>
       </c>
       <c r="E140" t="n">
-        <v>1455</v>
+        <v>1502</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H140" t="b">
@@ -5201,11 +5201,11 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>56223</v>
+        <v>56162</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Hans von Bühel: 'Die Königstochter von Frankreich</t>
+          <t>Steinhöwel, Heinrich: Apollonius</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5214,14 +5214,14 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="E141" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5235,11 +5235,11 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>56172</v>
+        <v>56170</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Kliges</t>
+          <t>Ulrich von Etzenbach: Alexander-Anhang</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1231</v>
+        <v>1253</v>
       </c>
       <c r="E142" t="n">
-        <v>1240</v>
+        <v>1297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -5269,11 +5269,11 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>56155</v>
+        <v>56171</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Der guote Gêrhart' (Prosaauflösung)</t>
+          <t>Ulrich von Etzenbach: Wilhelm von Wenden</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1221</v>
+        <v>1253</v>
       </c>
       <c r="E143" t="n">
-        <v>1250</v>
+        <v>1297</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -5303,11 +5303,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>56280</v>
+        <v>56175</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Orendel' ('Der Graue Rock')</t>
+          <t>Ulrich von Türheim: Tristan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5316,19 +5316,19 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1176</v>
+        <v>1231</v>
       </c>
       <c r="E144" t="n">
-        <v>1200</v>
+        <v>1243</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>storyverse</t>
         </is>
       </c>
       <c r="H144" t="b">
